--- a/Excel Assignment 1 - Data Exploration.xlsx
+++ b/Excel Assignment 1 - Data Exploration.xlsx
@@ -5,19 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83703c093884e9e4/Attachments/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83703c093884e9e4/Attachments/Desktop/Data Analytics/Assignments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D49C332-90AA-4CED-AF32-9603DA69C92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590A1191-DF4E-4676-95D8-68634FB30039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Dataset" sheetId="2" r:id="rId2"/>
+    <sheet name="Solutions" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Dataset!$A$1:$F$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Solutions!$A$1:$J$45</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="xxdYPntQl+bO0ka4qHfhA4BnM4OowOuFpS2wlv4H/kM="/>
     </ext>
@@ -26,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="121">
   <si>
     <t>Perform the following in the dataset from the 'Dataset' sheet.</t>
   </si>
@@ -356,13 +372,46 @@
   </si>
   <si>
     <t>Casio</t>
+  </si>
+  <si>
+    <t>Average Price</t>
+  </si>
+  <si>
+    <t>Minimum Price</t>
+  </si>
+  <si>
+    <t>Maximum Price</t>
+  </si>
+  <si>
+    <t>Price Range</t>
+  </si>
+  <si>
+    <t>The count of products with a price less than $100 using the COUNTIF function.</t>
+  </si>
+  <si>
+    <t>The total price for products in the 'Electronics' category using the SUMIF function.</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Country Code</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Product Price </t>
+  </si>
+  <si>
+    <t>Total Number of Products</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -403,8 +452,36 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -423,14 +500,8 @@
         <bgColor rgb="FFE0F7FA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -438,11 +509,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -451,12 +537,22 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -752,12 +848,12 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="9" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="9" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1766,6 +1862,7 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1774,15 +1871,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:F1000"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.109375" customWidth="1"/>
     <col min="3" max="6" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
@@ -1801,735 +1898,721 @@
       <c r="F1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>1000</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <v>30</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>80</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>15</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>130</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>40</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>900</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>25</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>70</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>20</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>200</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>45</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>30</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>5</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>90</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>35</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>500</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>50</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>130</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>10</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>950</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>25</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>90</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <v>40</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>120</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <v>35</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>150</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <v>15</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="7"/>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>250</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="6">
         <v>20</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>50</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <v>35</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>160</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="6">
         <v>15</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>980</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <v>10</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="6">
         <v>150</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="6">
         <v>15</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>200</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="7">
         <v>10</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="6">
         <v>700</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="6">
         <v>50</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <v>80</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="7">
         <v>20</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="6">
         <v>150</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="6">
         <v>30</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <v>50</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="7">
         <v>35</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="9"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="6">
         <v>800</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="6">
         <v>45</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>130</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="7">
         <v>25</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="6">
         <v>400</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="6">
         <v>40</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <v>230</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="7">
         <v>20</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G29" s="9"/>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="6">
         <v>60</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="6">
         <v>30</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="7">
         <v>40</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="7">
         <v>10</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G31" s="7"/>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="6">
         <v>130</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="6">
         <v>5</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <v>50</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="7">
         <v>50</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G33" s="7"/>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="6">
         <v>950</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="6">
         <v>25</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G34" s="7"/>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="7">
         <v>100</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="7">
         <v>20</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G35" s="7"/>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="13"/>
+      <c r="B38" s="13"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13"/>
+      <c r="B40" s="14"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13"/>
+      <c r="B41" s="13"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="15"/>
+      <c r="B43" s="13"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="15"/>
+      <c r="B44" s="13"/>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3484,5 +3567,1346 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE80CDCE-6473-48F7-9AA5-836BF929B618}">
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <f>IF(D2&gt;=500,"High Price","Standard Price")</f>
+        <v>High Price</v>
+      </c>
+      <c r="F2" s="6">
+        <v>30</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="str">
+        <f>LEFT(A2,2)</f>
+        <v>28</v>
+      </c>
+      <c r="I2" t="str">
+        <f>RIGHT(A2,2)</f>
+        <v>US</v>
+      </c>
+      <c r="J2" t="str">
+        <f>MID(A2,4,3)</f>
+        <v>JAN</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="7">
+        <v>80</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <f t="shared" ref="E3:E35" si="0">IF(D3&gt;=500,"High Price","Standard Price")</f>
+        <v>Standard Price</v>
+      </c>
+      <c r="F3" s="7">
+        <v>15</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H35" si="1">LEFT(A3,2)</f>
+        <v>15</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I35" si="2">RIGHT(A3,2)</f>
+        <v>US</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J35" si="3">MID(A3,4,3)</f>
+        <v>FEB</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="6">
+        <v>130</v>
+      </c>
+      <c r="E4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F4" s="6">
+        <v>40</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="1"/>
+        <v>03</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="2"/>
+        <v>US</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="3"/>
+        <v>MAR</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="7">
+        <v>900</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>High Price</v>
+      </c>
+      <c r="F5" s="7">
+        <v>25</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="2"/>
+        <v>US</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="3"/>
+        <v>APR</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="6">
+        <v>70</v>
+      </c>
+      <c r="E6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F6" s="6">
+        <v>20</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="2"/>
+        <v>US</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="3"/>
+        <v>MAY</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="7">
+        <v>200</v>
+      </c>
+      <c r="E7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F7" s="7">
+        <v>45</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="1"/>
+        <v>07</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="3"/>
+        <v>JUN</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="6">
+        <v>30</v>
+      </c>
+      <c r="E8" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F8" s="6">
+        <v>5</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="3"/>
+        <v>JUL</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="7">
+        <v>90</v>
+      </c>
+      <c r="E9" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F9" s="7">
+        <v>35</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="3"/>
+        <v>AUG</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="6">
+        <v>500</v>
+      </c>
+      <c r="E10" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>High Price</v>
+      </c>
+      <c r="F10" s="6">
+        <v>50</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="1"/>
+        <v>05</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="3"/>
+        <v>SEP</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="7">
+        <v>130</v>
+      </c>
+      <c r="E11" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F11" s="7">
+        <v>10</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="3"/>
+        <v>OCT</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="6">
+        <v>950</v>
+      </c>
+      <c r="E12" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>High Price</v>
+      </c>
+      <c r="F12" s="6">
+        <v>25</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="2"/>
+        <v>IN</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="3"/>
+        <v>JUN</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="7">
+        <v>90</v>
+      </c>
+      <c r="E13" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F13" s="7">
+        <v>40</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="2"/>
+        <v>AU</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="3"/>
+        <v>NOV</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="6">
+        <v>120</v>
+      </c>
+      <c r="E14" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F14" s="6">
+        <v>35</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="1"/>
+        <v>08</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="2"/>
+        <v>DE</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="3"/>
+        <v>DEC</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="7">
+        <v>150</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F15" s="7">
+        <v>15</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="3"/>
+        <v>FEB</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="6">
+        <v>250</v>
+      </c>
+      <c r="E16" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F16" s="6">
+        <v>20</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="2"/>
+        <v>ES</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="3"/>
+        <v>APR</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="7">
+        <v>50</v>
+      </c>
+      <c r="E17" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F17" s="7">
+        <v>35</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="3"/>
+        <v>AUG</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="6">
+        <v>160</v>
+      </c>
+      <c r="E18" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F18" s="6">
+        <v>15</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="2"/>
+        <v>CN</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="3"/>
+        <v>AUG</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="7">
+        <v>980</v>
+      </c>
+      <c r="E19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>High Price</v>
+      </c>
+      <c r="F19" s="7">
+        <v>10</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="2"/>
+        <v>IT</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="3"/>
+        <v>JAN</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="6">
+        <v>150</v>
+      </c>
+      <c r="E20" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F20" s="6">
+        <v>15</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="1"/>
+        <v>01</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="2"/>
+        <v>UK</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="3"/>
+        <v>MAR</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="7">
+        <v>200</v>
+      </c>
+      <c r="E21" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F21" s="7">
+        <v>10</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="2"/>
+        <v>US</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="3"/>
+        <v>AUG</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="6">
+        <v>700</v>
+      </c>
+      <c r="E22" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>High Price</v>
+      </c>
+      <c r="F22" s="6">
+        <v>50</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="2"/>
+        <v>RU</v>
+      </c>
+      <c r="J22" t="str">
+        <f t="shared" si="3"/>
+        <v>MAY</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="7">
+        <v>80</v>
+      </c>
+      <c r="E23" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F23" s="7">
+        <v>20</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="1"/>
+        <v>09</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+      <c r="J23" t="str">
+        <f t="shared" si="3"/>
+        <v>JAN</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="6">
+        <v>150</v>
+      </c>
+      <c r="E24" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F24" s="6">
+        <v>30</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="2"/>
+        <v>BR</v>
+      </c>
+      <c r="J24" t="str">
+        <f t="shared" si="3"/>
+        <v>JUL</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="7">
+        <v>50</v>
+      </c>
+      <c r="E25" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F25" s="7">
+        <v>35</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+      <c r="J25" t="str">
+        <f t="shared" si="3"/>
+        <v>AUG</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="6">
+        <v>800</v>
+      </c>
+      <c r="E26" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>High Price</v>
+      </c>
+      <c r="F26" s="6">
+        <v>45</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+      <c r="J26" t="str">
+        <f t="shared" si="3"/>
+        <v>SEP</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="7">
+        <v>130</v>
+      </c>
+      <c r="E27" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F27" s="7">
+        <v>25</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="1"/>
+        <v>03</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+      <c r="J27" t="str">
+        <f t="shared" si="3"/>
+        <v>JUN</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="6">
+        <v>400</v>
+      </c>
+      <c r="E28" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F28" s="6">
+        <v>40</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" si="3"/>
+        <v>JUL</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="7">
+        <v>230</v>
+      </c>
+      <c r="E29" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F29" s="7">
+        <v>20</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="2"/>
+        <v>ES</v>
+      </c>
+      <c r="J29" t="str">
+        <f t="shared" si="3"/>
+        <v>APR</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="6">
+        <v>60</v>
+      </c>
+      <c r="E30" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F30" s="6">
+        <v>30</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="1"/>
+        <v>07</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="3"/>
+        <v>MAR</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" s="7">
+        <v>40</v>
+      </c>
+      <c r="E31" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F31" s="7">
+        <v>10</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="3"/>
+        <v>APR</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="6">
+        <v>130</v>
+      </c>
+      <c r="E32" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F32" s="6">
+        <v>5</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+      <c r="J32" t="str">
+        <f t="shared" si="3"/>
+        <v>MAY</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" s="7">
+        <v>50</v>
+      </c>
+      <c r="E33" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F33" s="7">
+        <v>50</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="1"/>
+        <v>02</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="2"/>
+        <v>CA</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="3"/>
+        <v>DEC</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="6">
+        <v>950</v>
+      </c>
+      <c r="E34" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>High Price</v>
+      </c>
+      <c r="F34" s="6">
+        <v>25</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="2"/>
+        <v>IN</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="3"/>
+        <v>JUN</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="7">
+        <v>100</v>
+      </c>
+      <c r="E35" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>Standard Price</v>
+      </c>
+      <c r="F35" s="7">
+        <v>20</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="1"/>
+        <v>09</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="2"/>
+        <v>FR</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="3"/>
+        <v>JUL</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E39" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" s="12">
+        <f>SUM(D2:D35)</f>
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E40" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F40" s="12">
+        <f>COUNT(F2:F35)</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E41" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F41" s="12">
+        <f>ROUND(AVERAGE(D2:D35),2)</f>
+        <v>297.06</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E42" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F42" s="12">
+        <f>MIN(D2:D35)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E43" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F43" s="12">
+        <f>MAX(D2:D35)</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="62.4" x14ac:dyDescent="0.25">
+      <c r="E44" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F44" s="12">
+        <f>COUNTIF(D2:D35,"&lt;100")</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="62.4" x14ac:dyDescent="0.25">
+      <c r="E45" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F45" s="12">
+        <f>SUMIF(G2:G35,G2,D2:D35)</f>
+        <v>8050</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="68" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>